--- a/results/Int All Data -0.8/Rando_8_permute.xlsx
+++ b/results/Int All Data -0.8/Rando_8_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7230342764804222</v>
+        <v>0.7229936165683034</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7233105195743448</v>
+        <v>0.7233094725379812</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7211422817714459</v>
+        <v>0.7240589760682389</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.720826425801768</v>
+        <v>0.7199518014260635</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7151431124202943</v>
+        <v>0.7226371006865069</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7151431124202943</v>
+        <v>0.7226371006865069</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7160906803293279</v>
+        <v>0.7226371006865069</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7141173657961142</v>
+        <v>0.7171508046474454</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.71526195104756</v>
+        <v>0.7195192009018473</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.71526195104756</v>
+        <v>0.7197172652806232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7149471421142456</v>
+        <v>0.7178242235352834</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7146312861445678</v>
+        <v>0.7178242235352834</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7140787999567225</v>
+        <v>0.7162449436868943</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7150670277778748</v>
+        <v>0.712848706735585</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7174739898716682</v>
+        <v>0.714938765823337</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7153026109596787</v>
+        <v>0.7197162182442596</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7145541544657846</v>
+        <v>0.7200310271775738</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7164878561232432</v>
+        <v>0.7181369383958704</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7164878561232432</v>
+        <v>0.7098923995630368</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7151066406536299</v>
+        <v>0.7103260471236166</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7185403964079673</v>
+        <v>0.7088666529388565</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7148293505233436</v>
+        <v>0.7081953281237457</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7125380859477249</v>
+        <v>0.7081953281237457</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7123410686053127</v>
+        <v>0.7074854374692433</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7002259853484711</v>
+        <v>0.7077616805631659</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6991616728848993</v>
+        <v>0.7070100829601813</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7085956450267518</v>
+        <v>0.7064575967723359</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7085956450267518</v>
+        <v>0.7163669234232505</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7017228983362592</v>
+        <v>0.6996755932333529</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6990000802727878</v>
+        <v>0.7022013939544121</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7000664868090869</v>
+        <v>0.6965566464123298</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6978877786425522</v>
+        <v>0.6935169253428172</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6965847418880857</v>
+        <v>0.6905553829884512</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7032135291058659</v>
+        <v>0.6873978703280366</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7056215382360229</v>
+        <v>0.6848335037675859</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7034032171937331</v>
+        <v>0.6848335037675859</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7090865305752069</v>
+        <v>0.6845572606736632</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7094023865448846</v>
+        <v>0.6873999644007636</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.709837081141828</v>
+        <v>0.6844790819585164</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7146927122778974</v>
+        <v>0.6858206845523744</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.711574812493238</v>
+        <v>0.6872019000219878</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.705341106996646</v>
+        <v>0.6896495220279</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7177730932595289</v>
+        <v>0.6961626117275053</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7167890535838309</v>
+        <v>0.6924526128792452</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7208513801684333</v>
+        <v>0.6939912328155157</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.725630926662083</v>
+        <v>0.6939912328155157</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7259071697560056</v>
+        <v>0.6939912328155157</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7201029236745393</v>
+        <v>0.6906731745793531</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7201029236745393</v>
+        <v>0.6866816974553527</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7196692761139594</v>
+        <v>0.6869621286947296</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7195118716473023</v>
+        <v>0.6871580990007784</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7135523151719059</v>
+        <v>0.6856173849917808</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7083797810297952</v>
+        <v>0.6795744146194198</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7044727648391229</v>
+        <v>0.6568120185814053</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6487433818576519</v>
+        <v>0.6561021279269029</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6494928853879096</v>
+        <v>0.6568912443329157</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6494928853879096</v>
+        <v>0.6546395926330522</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6095604890357842</v>
+        <v>0.6557445650087428</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6129150190386112</v>
+        <v>0.6525474394725729</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6020153704938173</v>
+        <v>0.6525474394725729</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6020153704938173</v>
+        <v>0.6527465508877124</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6020153704938173</v>
+        <v>0.6517208042635321</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6010667555484203</v>
+        <v>0.645840473539646</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.601027142672665</v>
+        <v>0.6522732904513774</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6034768587513044</v>
+        <v>0.6432000223367758</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5970409007304823</v>
+        <v>0.6404365443611857</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5904808689005769</v>
+        <v>0.6691178369624777</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5946630811488083</v>
+        <v>0.6564898803935461</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5972691546577413</v>
+        <v>0.6512026957696241</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5619609944053356</v>
+        <v>0.644418598157914</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5595508912024515</v>
+        <v>0.659622264181235</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5675233750868167</v>
+        <v>0.66720490152623</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5658221155020714</v>
+        <v>0.6698912478230369</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.55406459516339</v>
+        <v>0.6793220788557987</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5563548127026452</v>
+        <v>0.6749011423166726</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5519005455059454</v>
+        <v>0.6749011423166726</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5143386394809492</v>
+        <v>0.6749011423166726</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5107453851872276</v>
+        <v>0.6731206569804169</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5139414636870339</v>
+        <v>0.6191654771170203</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.504347993005797</v>
+        <v>0.6207843698411646</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5035588765997844</v>
+        <v>0.6129275834749741</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5044689257057897</v>
+        <v>0.6011585457362933</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5044689257057897</v>
+        <v>0.6011585457362933</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4985875479455402</v>
+        <v>0.601833011660495</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4961013601002363</v>
+        <v>0.5462371258153795</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4983123518879811</v>
+        <v>0.5424030531580362</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4992557316515603</v>
+        <v>0.5337841988252252</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4964922536759702</v>
+        <v>0.5387565745158329</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4964922536759702</v>
+        <v>0.5387961873915881</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.4935724182700865</v>
+        <v>0.5254853886075463</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.4938100955246176</v>
+        <v>0.5220130670138173</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.4940456787064215</v>
+        <v>0.5141927524142913</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.4964922536759702</v>
+        <v>0.5090233593812713</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.4960992660275091</v>
+        <v>0.5092996024751939</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.498267503830408</v>
+        <v>0.5092996024751939</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5000427539848459</v>
+        <v>0.5220558209986633</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.4984249082970652</v>
+        <v>0.520556813938148</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4978724221092198</v>
+        <v>0.5132118538476842</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.4968862883607948</v>
+        <v>0.5144002401203394</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.4985437469243307</v>
+        <v>0.5125468112507547</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.4953883283366431</v>
+        <v>0.5132181360658656</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4972031913668362</v>
+        <v>0.5147171431263808</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.4965329135880889</v>
+        <v>0.5180727201655714</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4973595487971297</v>
+        <v>0.4861943020281094</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5010278406969074</v>
+        <v>0.4742804242591345</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5010278406969074</v>
+        <v>0.4742804242591345</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5004753545090621</v>
+        <v>0.4562558677662875</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.4955415446578459</v>
+        <v>0.4815075927586965</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4938840860943101</v>
+        <v>0.4817848828889827</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4980277325031498</v>
+        <v>0.4864956739947578</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5006317119393556</v>
+        <v>0.487801851858315</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5006317119393556</v>
+        <v>0.4887890326431037</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5006713248151108</v>
+        <v>0.4812898091950734</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5006713248151108</v>
+        <v>0.4816056651647512</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5006713248151108</v>
+        <v>0.4498855240242494</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.500355468845433</v>
+        <v>0.4489390031515794</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4997237569060773</v>
+        <v>0.4621246810901743</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.499171270718232</v>
+        <v>0.4648078862778904</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5</v>
+        <v>0.4583698341843412</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4997237569060773</v>
+        <v>0.4762359391741675</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4994475138121547</v>
+        <v>0.4762359391741675</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4994475138121547</v>
+        <v>0.4721746596259289</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4994475138121547</v>
+        <v>0.4775400229649976</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4994475138121547</v>
+        <v>0.4712187154259868</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4994475138121547</v>
+        <v>0.4728793150986134</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4997237569060773</v>
+        <v>0.4862901058553764</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4997237569060773</v>
+        <v>0.4916961291065639</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4997237569060773</v>
+        <v>0.4948140288912234</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4997237569060773</v>
+        <v>0.4941062323094481</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4997237569060773</v>
+        <v>0.5004191635575503</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.4980048722092118</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.4985990653455395</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.4899938224854549</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.4899938224854549</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.4899938224854549</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5</v>
+        <v>0.4904670829217899</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.4904670829217899</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.4979694474789109</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.5084239310631259</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.5013948269423397</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.4989472049364275</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.5111383728356886</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.5106651123993536</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.5050599777330267</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.5050599777330267</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.5022130858604719</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.5022130858604719</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.5022130858604719</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.5028051849240724</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.5028051849240724</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.5011060194120541</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.5011060194120541</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.5013030367544665</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.5003950817211882</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.5003950817211882</v>
       </c>
     </row>
   </sheetData>
